--- a/TestCases/Medical_TestCase.xlsx
+++ b/TestCases/Medical_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445EF516-2D63-49D5-A4C9-06B9BD16C010}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71587F0F-C42A-4B20-9D15-6B825A86DD3C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,18 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
   <si>
     <t>TEST CASE</t>
-  </si>
-  <si>
-    <t>System Name：</t>
-  </si>
-  <si>
-    <t>SpringMediCareWeb</t>
-  </si>
-  <si>
-    <t>Module Code：</t>
   </si>
   <si>
     <t>Test requirement:</t>
@@ -74,6 +65,15 @@
   </si>
   <si>
     <t>Note</t>
+  </si>
+  <si>
+    <t>System Name：</t>
+  </si>
+  <si>
+    <t>SpringMediCareWeb</t>
+  </si>
+  <si>
+    <t>Module Code：</t>
   </si>
   <si>
     <t>Retest Date</t>
@@ -268,29 +268,89 @@
     <t>TC-MEDICAL-007</t>
   </si>
   <si>
-    <t>Bác sĩ không được xem hoặc cập nhật hồ sơ bệnh án không thuộc mình.</t>
+    <t>Bác sĩ không được xem hồ sơ bệnh án không thuộc mình.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị hồ sơ bệnh án thuộc bác sĩ thứ nhất.
-2: Đăng nhập bằng tài khoản bác sĩ thứ hai.
+    <t>1: Chuẩn bị hồ sơ bệnh án thuộc bác sĩ Ly Minh.
+2: Đăng nhập bằng tài khoản bác sĩ Tran Binh.
 3: Mở trang Lịch hẹn bệnh nhân.
-4: Kiểm tra lịch có xuất hiện hay không.
-5: Nhập trực tiếp URL xem hồ sơ của lịch đó.
-6: Thử mở chức năng Cập nhật hồ sơ nếu trang vẫn hiển thị.
-7: Kiểm tra phản hồi của hệ thống và dữ liệu hồ sơ.</t>
+4: Kiểm tra lịch đó không xuất hiện trong danh sách.
+5: Nhập trực tiếp URL xem hồ sơ bệnh án.
+6: Kiểm tra nội dung trang được hiển thị.
+7: Kiểm tra dữ liệu hồ sơ có bị thay đổi hay không.</t>
   </si>
   <si>
-    <t>Lịch và hồ sơ không xuất hiện trong danh sách của bác sĩ khác.
-Bác sĩ khác không được mở hoặc cập nhật hồ sơ.
-Hệ thống hiển thị thông báo không có quyền hoặc chuyển hướng.
-Nội dung hồ sơ không bị thay đổi.
-Không tạo thêm hồ sơ bệnh án mới.</t>
+    <t>Hồ sơ không xuất hiện trong danh sách của bác sĩ Tran Binh. Khi truy cập trực tiếp URL, hệ thống chặn truy cập hoặc hiển thị thông báo không có quyền. Thông tin bệnh nhân và nội dung hồ sơ không được hiển thị. Dữ liệu hồ sơ không thay đổi.</t>
   </si>
   <si>
     <t>TCMedical7</t>
   </si>
   <si>
-    <t>Hệ thống chưa kiểm tra quyền bác sĩ khi truy cập hồ sơ bệnh án, nên bác sĩ khác vẫn xem được chi tiết hồ sơ không thuộc mình.</t>
+    <t>Hệ thống chưa kiểm tra quyền xem hồ sơ, nên bác sĩ Tran Binh vẫn xem được chi tiết hồ sơ thuộc bác sĩ Ly Minh.</t>
+  </si>
+  <si>
+    <t>TCMedicalRetest7</t>
+  </si>
+  <si>
+    <t>TC-MEDICAL-008</t>
+  </si>
+  <si>
+    <t>Bác sĩ không được cập nhật hồ sơ bệnh án không thuộc mình.</t>
+  </si>
+  <si>
+    <t>1: Chuẩn bị hồ sơ bệnh án của lịch TC-MEDICAL-008 thuộc bác sĩ Ly Minh.
+2: Đăng nhập bằng tài khoản bác sĩ Tran Binh.
+3: Nhập trực tiếp URL xem hồ sơ của lịch TC-MEDICAL-008.
+4: Kiểm tra thông tin bác sĩ phụ trách trên hồ sơ.
+5: Nhấn nút Cập nhật hồ sơ.
+6: Thay đổi chẩn đoán và hướng điều trị.
+7: Nhấn nút Lưu thay đổi.
+8: Kiểm tra thông báo và nội dung hồ sơ sau khi lưu.</t>
+  </si>
+  <si>
+    <t>Hệ thống không cho phép bác sĩ Tran Binh cập nhật hồ sơ thuộc bác sĩ Ly Minh.
+Nút Cập nhật hồ sơ không được hiển thị hoặc thao tác cập nhật bị chặn.
+Hệ thống hiển thị thông báo không có quyền.
+Chẩn đoán và hướng điều trị cũ không bị thay đổi.
+Hồ sơ vẫn thuộc đúng bác sĩ Ly Minh.</t>
+  </si>
+  <si>
+    <t>TCMedical8_1, TCMedical8_2, TCMedical8_3</t>
+  </si>
+  <si>
+    <t>Hệ thống chưa kiểm tra quyền sở hữu hồ sơ khi cập nhật. Bác sĩ Tran Binh vẫn mở được chức năng Cập nhật hồ sơ thuộc bác sĩ Ly Minh, thay đổi dữ liệu và lưu thành công.</t>
+  </si>
+  <si>
+    <t>TCMedicalRetest8</t>
+  </si>
+  <si>
+    <t>TC-MEDICAL-009</t>
+  </si>
+  <si>
+    <t>Hủy cập nhật hồ sơ bệnh án không làm thay đổi dữ liệu đã lưu.</t>
+  </si>
+  <si>
+    <t>1: Chuẩn bị lịch TC-MEDICAL-009 ở trạng thái Đã hoàn thành và đã có hồ sơ bệnh án.
+2: Đăng nhập bằng đúng tài khoản bác sĩ Ly Minh.
+3: Mở trang Lịch hẹn bệnh nhân.
+4: Tìm lịch TC-MEDICAL-009 và nhấn nút Xem hồ sơ.
+5: Nhấn nút Cập nhật hồ sơ.
+6: Thay đổi chẩn đoán và hướng điều trị bằng nội dung mới.
+7: Nhấn nút Hủy.
+8: Kiểm tra nội dung hồ sơ bệnh án sau khi hủy.</t>
+  </si>
+  <si>
+    <t>Hệ thống hủy thao tác cập nhật và đóng form chỉnh sửa.
+Dữ liệu mới nhập không được lưu.
+Chẩn đoán và hướng điều trị cũ vẫn được giữ nguyên.
+Hồ sơ vẫn thuộc đúng bệnh nhân, bác sĩ và lịch hẹn.
+Trạng thái lịch vẫn là Đã hoàn thành.</t>
+  </si>
+  <si>
+    <t>TCMedical9_1, TCMedical9_2, TCMedical9_3</t>
+  </si>
+  <si>
+    <t>Hệ thống hủy thao tác cập nhật thành công, không lưu dữ liệu tạm và giữ nguyên nội dung hồ sơ bệnh án ban đầu.</t>
   </si>
 </sst>
 </file>
@@ -298,9 +358,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="d\-m"/>
+    <numFmt numFmtId="166" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -313,6 +373,10 @@
       <name val="Tahoma"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="MS PGothic"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,10 +386,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="MS PGothic"/>
     </font>
     <font>
       <b/>
@@ -348,6 +408,12 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Tahoma"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -388,36 +454,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -445,7 +487,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -455,26 +499,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -517,9 +541,7 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -538,99 +560,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -854,7 +903,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA998"/>
+  <dimension ref="A1:AA1001"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -873,9 +922,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -902,9 +951,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -931,13 +980,13 @@
     </row>
     <row r="3" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
-      <c r="B3" s="32" t="s">
-        <v>2</v>
+      <c r="B3" s="37" t="s">
+        <v>15</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="27"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="32"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -964,13 +1013,13 @@
     </row>
     <row r="4" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="27"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -997,13 +1046,13 @@
     </row>
     <row r="5" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="27"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1030,13 +1079,13 @@
     </row>
     <row r="6" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1067,16 +1116,16 @@
     </row>
     <row r="7" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1132,39 +1181,39 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="H9" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="I9" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="34" t="s">
+      <c r="J9" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="42" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="3"/>
@@ -1183,19 +1232,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1213,18 +1262,18 @@
     </row>
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="42"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1241,21 +1290,21 @@
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="27"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="32"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1281,11 +1330,11 @@
       <c r="C13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
       <c r="G13" s="17" t="s">
         <v>27</v>
       </c>
@@ -1293,7 +1342,7 @@
         <v>46233</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>28</v>
@@ -1326,11 +1375,11 @@
       <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
       <c r="G14" s="17" t="s">
         <v>33</v>
       </c>
@@ -1338,7 +1387,7 @@
         <v>46233</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>34</v>
@@ -1371,11 +1420,11 @@
       <c r="C15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="17" t="s">
         <v>39</v>
       </c>
@@ -1383,7 +1432,7 @@
         <v>46233</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>40</v>
@@ -1416,11 +1465,11 @@
       <c r="C16" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
       <c r="G16" s="17" t="s">
         <v>45</v>
       </c>
@@ -1428,7 +1477,7 @@
         <v>46233</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>46</v>
@@ -1452,21 +1501,21 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="27"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="32"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1492,11 +1541,11 @@
       <c r="C18" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
       <c r="G18" s="17" t="s">
         <v>52</v>
       </c>
@@ -1504,14 +1553,14 @@
         <v>46233</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>53</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="14"/>
-      <c r="M18" s="22"/>
+      <c r="M18" s="23"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -1528,21 +1577,21 @@
       <c r="AA18" s="3"/>
     </row>
     <row r="19" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="27"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="32"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -1568,19 +1617,19 @@
       <c r="C20" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="24" t="s">
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="25" t="s">
         <v>59</v>
       </c>
       <c r="H20" s="18">
         <v>46233</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>60</v>
@@ -1613,11 +1662,11 @@
       <c r="C21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D21" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
       <c r="G21" s="17" t="s">
         <v>65</v>
       </c>
@@ -1625,14 +1674,20 @@
         <v>46233</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="K21" s="18"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="22"/>
+      <c r="K21" s="18">
+        <v>46234</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>67</v>
+      </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
@@ -1648,20 +1703,42 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
+    <row r="22" spans="1:27" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="18">
+        <v>46233</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="K22" s="18">
+        <v>46234</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>74</v>
+      </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
@@ -1677,20 +1754,36 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+    <row r="23" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="18">
+        <v>46233</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="K23" s="18"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="23"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1706,20 +1799,20 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
+    <row r="24" spans="1:27" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="29"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
@@ -1737,7 +1830,7 @@
     </row>
     <row r="25" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
-      <c r="B25" s="21"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1824,7 +1917,7 @@
     </row>
     <row r="28" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+      <c r="B28" s="22"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -2002,7 +2095,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="23"/>
+      <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -2089,7 +2182,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="24"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -2351,7 +2444,7 @@
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
-      <c r="G46" s="21"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
@@ -2438,7 +2531,7 @@
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="G49" s="22"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
@@ -29981,27 +30074,116 @@
       <c r="Z998" s="3"/>
       <c r="AA998" s="3"/>
     </row>
+    <row r="999" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A999" s="3"/>
+      <c r="B999" s="3"/>
+      <c r="C999" s="3"/>
+      <c r="D999" s="3"/>
+      <c r="E999" s="3"/>
+      <c r="F999" s="3"/>
+      <c r="G999" s="3"/>
+      <c r="H999" s="3"/>
+      <c r="I999" s="3"/>
+      <c r="J999" s="3"/>
+      <c r="K999" s="3"/>
+      <c r="L999" s="3"/>
+      <c r="M999" s="3"/>
+      <c r="N999" s="3"/>
+      <c r="O999" s="3"/>
+      <c r="P999" s="3"/>
+      <c r="Q999" s="3"/>
+      <c r="R999" s="3"/>
+      <c r="S999" s="3"/>
+      <c r="T999" s="3"/>
+      <c r="U999" s="3"/>
+      <c r="V999" s="3"/>
+      <c r="W999" s="3"/>
+      <c r="X999" s="3"/>
+      <c r="Y999" s="3"/>
+      <c r="Z999" s="3"/>
+      <c r="AA999" s="3"/>
+    </row>
+    <row r="1000" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A1000" s="3"/>
+      <c r="B1000" s="3"/>
+      <c r="C1000" s="3"/>
+      <c r="D1000" s="3"/>
+      <c r="E1000" s="3"/>
+      <c r="F1000" s="3"/>
+      <c r="G1000" s="3"/>
+      <c r="H1000" s="3"/>
+      <c r="I1000" s="3"/>
+      <c r="J1000" s="3"/>
+      <c r="K1000" s="3"/>
+      <c r="L1000" s="3"/>
+      <c r="M1000" s="3"/>
+      <c r="N1000" s="3"/>
+      <c r="O1000" s="3"/>
+      <c r="P1000" s="3"/>
+      <c r="Q1000" s="3"/>
+      <c r="R1000" s="3"/>
+      <c r="S1000" s="3"/>
+      <c r="T1000" s="3"/>
+      <c r="U1000" s="3"/>
+      <c r="V1000" s="3"/>
+      <c r="W1000" s="3"/>
+      <c r="X1000" s="3"/>
+      <c r="Y1000" s="3"/>
+      <c r="Z1000" s="3"/>
+      <c r="AA1000" s="3"/>
+    </row>
+    <row r="1001" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A1001" s="3"/>
+      <c r="B1001" s="3"/>
+      <c r="C1001" s="3"/>
+      <c r="D1001" s="3"/>
+      <c r="E1001" s="3"/>
+      <c r="F1001" s="3"/>
+      <c r="G1001" s="3"/>
+      <c r="H1001" s="3"/>
+      <c r="I1001" s="3"/>
+      <c r="J1001" s="3"/>
+      <c r="K1001" s="3"/>
+      <c r="L1001" s="3"/>
+      <c r="M1001" s="3"/>
+      <c r="N1001" s="3"/>
+      <c r="O1001" s="3"/>
+      <c r="P1001" s="3"/>
+      <c r="Q1001" s="3"/>
+      <c r="R1001" s="3"/>
+      <c r="S1001" s="3"/>
+      <c r="T1001" s="3"/>
+      <c r="U1001" s="3"/>
+      <c r="V1001" s="3"/>
+      <c r="W1001" s="3"/>
+      <c r="X1001" s="3"/>
+      <c r="Y1001" s="3"/>
+      <c r="Z1001" s="3"/>
+      <c r="AA1001" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="D20:F20"/>
+  <mergeCells count="28">
     <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D9:F10"/>
+    <mergeCell ref="B11:M11"/>
+    <mergeCell ref="A12:M12"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A17:M17"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
     <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D9:F10"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="B11:M11"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
@@ -30018,6 +30200,10 @@
     <hyperlink ref="G18" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
     <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
     <hyperlink ref="G21" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
+    <hyperlink ref="M21" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
+    <hyperlink ref="G22" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
+    <hyperlink ref="M22" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
+    <hyperlink ref="G23" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestCases/Medical_TestCase.xlsx
+++ b/TestCases/Medical_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71587F0F-C42A-4B20-9D15-6B825A86DD3C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F30B792-D8B3-43E3-8D7D-A99304DB8E7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,7 +358,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="d\-m"/>
+    <numFmt numFmtId="164" formatCode="d\-m"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -621,7 +621,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -649,38 +649,38 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -922,9 +922,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -951,9 +951,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -982,11 +982,11 @@
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="32"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="38"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1015,11 +1015,11 @@
       <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="32"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="38"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1048,11 +1048,11 @@
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="32"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1181,39 +1181,39 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="39" t="s">
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="42" t="s">
+      <c r="J9" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="42" t="s">
+      <c r="K9" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="42" t="s">
+      <c r="L9" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="42" t="s">
+      <c r="M9" s="39" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="3"/>
@@ -1232,19 +1232,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
+      <c r="A10" s="40"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1262,18 +1262,18 @@
     </row>
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1290,21 +1290,21 @@
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="32"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="38"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1330,11 +1330,11 @@
       <c r="C13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
       <c r="G13" s="17" t="s">
         <v>27</v>
       </c>
@@ -1375,11 +1375,11 @@
       <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
       <c r="G14" s="17" t="s">
         <v>33</v>
       </c>
@@ -1420,11 +1420,11 @@
       <c r="C15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
       <c r="G15" s="17" t="s">
         <v>39</v>
       </c>
@@ -1465,11 +1465,11 @@
       <c r="C16" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
       <c r="G16" s="17" t="s">
         <v>45</v>
       </c>
@@ -1501,21 +1501,21 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="32"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="38"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1541,11 +1541,11 @@
       <c r="C18" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
       <c r="G18" s="17" t="s">
         <v>52</v>
       </c>
@@ -1577,21 +1577,21 @@
       <c r="AA18" s="3"/>
     </row>
     <row r="19" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="32"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="38"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -1617,11 +1617,11 @@
       <c r="C20" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
       <c r="G20" s="25" t="s">
         <v>59</v>
       </c>
@@ -1662,11 +1662,11 @@
       <c r="C21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D21" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
       <c r="G21" s="17" t="s">
         <v>65</v>
       </c>
@@ -1713,11 +1713,11 @@
       <c r="C22" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
       <c r="G22" s="17" t="s">
         <v>72</v>
       </c>
@@ -1754,7 +1754,7 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="191.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>75</v>
       </c>
@@ -1764,11 +1764,11 @@
       <c r="C23" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
       <c r="G23" s="17" t="s">
         <v>79</v>
       </c>
@@ -30163,6 +30163,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="D23:F23"/>
@@ -30179,18 +30191,6 @@
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>

--- a/TestCases/Medical_TestCase.xlsx
+++ b/TestCases/Medical_TestCase.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F30B792-D8B3-43E3-8D7D-A99304DB8E7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B562A163-4BA8-4962-9B81-22B7184455B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MEDICAL" sheetId="7" r:id="rId1"/>
+    <sheet name="MEDICAL" sheetId="8" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -26,6 +26,15 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
   <si>
     <t>TEST CASE</t>
+  </si>
+  <si>
+    <t>System Name：</t>
+  </si>
+  <si>
+    <t>SpringMediCareWeb</t>
+  </si>
+  <si>
+    <t>Module Code：</t>
   </si>
   <si>
     <t>Test requirement:</t>
@@ -67,15 +76,6 @@
     <t>Note</t>
   </si>
   <si>
-    <t>System Name：</t>
-  </si>
-  <si>
-    <t>SpringMediCareWeb</t>
-  </si>
-  <si>
-    <t>Module Code：</t>
-  </si>
-  <si>
     <t>Retest Date</t>
   </si>
   <si>
@@ -85,10 +85,10 @@
     <t>Retest Evidence</t>
   </si>
   <si>
-    <t>MEDICAL400 - Medical Record Management</t>
+    <t>MEDICAL - Medical Record Management</t>
   </si>
   <si>
-    <t>MEDICAL1 - Examination and Medical Record Management</t>
+    <t>Medical Record Management</t>
   </si>
   <si>
     <t>1. Kiểm tra tạo hồ sơ bệnh án</t>
@@ -100,14 +100,14 @@
     <t>Bác sĩ tạo hồ sơ bệnh án thành công cho lịch hẹn đã được xác nhận.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch hẹn trạng thái Đã xác nhận và chưa có hồ sơ bệnh án.
-2: Đăng nhập bằng đúng tài khoản bác sĩ của lịch.
-3: Mở trang Lịch hẹn bệnh nhân.
-4: Tìm lịch TC-MEDICAL-001.
-5: Nhấn nút Khám bệnh.
+    <t>1: Chuẩn bị một lịch hẹn Đã xác nhận, chưa có hồ sơ bệnh án và ghi nhận thông tin lịch.
+2: Đăng nhập bằng bác sĩ phụ trách lịch hẹn.
+3: Mở trang Lịch hẹn bệnh nhân và tìm đúng lịch vừa chuẩn bị.
+4: Nhấn Khám bệnh.
+5: Kiểm tra trang Khám bệnh được mở đúng cho lịch hẹn.
 6: Nhập chẩn đoán và hướng điều trị hợp lệ.
-7: Nhấn nút Lưu hồ sơ bệnh án.
-8: Kiểm tra hồ sơ và trạng thái lịch sau khi lưu.</t>
+7: Nhấn Lưu hồ sơ bệnh án.
+8: Kiểm tra hồ sơ được tạo đúng và lịch chuyển sang Đã hoàn thành.</t>
   </si>
   <si>
     <t>Hệ thống tạo hồ sơ bệnh án thành công.
@@ -129,13 +129,12 @@
     <t>Không cho phép bác sĩ tạo hồ sơ bệnh án khi bỏ trống chẩn đoán.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch hẹn trạng thái Đã xác nhận và chưa có hồ sơ bệnh án.
-2: Đăng nhập bằng đúng tài khoản bác sĩ của lịch.
-3: Mở trang Khám bệnh của lịch TC-MEDICAL-002.
-4: Để trống trường Chẩn đoán.
-5: Nhập hướng điều trị hợp lệ.
-6: Nhấn nút Lưu hồ sơ bệnh án.
-7: Kiểm tra thông báo và trạng thái lịch.</t>
+    <t>1: Chuẩn bị lịch Đã xác nhận, chưa có hồ sơ bệnh án.
+2: Đăng nhập bằng bác sĩ phụ trách và mở trang Khám bệnh của lịch.
+3: Để trống Chẩn đoán và nhập Hướng điều trị hợp lệ.
+4: Nhấn Lưu hồ sơ bệnh án.
+5: Kiểm tra thông báo validation của trường Chẩn đoán.
+6: Kiểm tra không tạo hồ sơ mới và lịch vẫn Đã xác nhận.</t>
   </si>
   <si>
     <t>Hệ thống hiển thị thông báo yêu cầu nhập đầy đủ chẩn đoán.
@@ -156,13 +155,12 @@
     <t>Không cho phép bác sĩ tạo hồ sơ bệnh án khi bỏ trống hướng điều trị.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch hẹn trạng thái Đã xác nhận và chưa có hồ sơ bệnh án.
-2: Đăng nhập bằng đúng tài khoản bác sĩ của lịch.
-3: Mở trang Khám bệnh của lịch TC-MEDICAL-003.
-4: Nhập chẩn đoán hợp lệ.
-5: Để trống trường Hướng điều trị.
-6: Nhấn nút Lưu hồ sơ bệnh án.
-7: Kiểm tra thông báo và trạng thái lịch.</t>
+    <t>1: Chuẩn bị lịch Đã xác nhận, chưa có hồ sơ bệnh án.
+2: Đăng nhập bằng bác sĩ phụ trách và mở trang Khám bệnh của lịch.
+3: Nhập Chẩn đoán hợp lệ và để trống Hướng điều trị.
+4: Nhấn Lưu hồ sơ bệnh án.
+5: Kiểm tra thông báo validation của trường Hướng điều trị.
+6: Kiểm tra không tạo hồ sơ mới và lịch vẫn Đã xác nhận.</t>
   </si>
   <si>
     <t>Hệ thống hiển thị thông báo yêu cầu nhập đầy đủ hướng điều trị.
@@ -183,14 +181,13 @@
     <t>Không cho phép tạo thêm hồ sơ bệnh án cho lịch đã hoàn thành và đã có hồ sơ.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch TC-MEDICAL-004 ở trạng thái Đã hoàn thành và đã có hồ sơ bệnh án.
-2: Đăng nhập bằng đúng tài khoản bác sĩ của lịch.
-3: Mở trang Lịch hẹn bệnh nhân.
-4: Tìm lịch TC-MEDICAL-004 và nhấn nút Xem hồ sơ.
-5: Kiểm tra hồ sơ bệnh án hiện có được hiển thị đúng.
-6: Sao chép appointmentId của lịch.
-7: Nhập trực tiếp URL trang Khám bệnh với appointmentId đó.
-8: Kiểm tra hệ thống có chặn form tạo hồ sơ mới hay không.</t>
+    <t>1: Chuẩn bị lịch Đã hoàn thành và đã có hồ sơ bệnh án; ghi nhận appointmentId và nội dung hồ sơ hiện tại.
+2: Đăng nhập bằng bác sĩ phụ trách.
+3: Mở Lịch hẹn bệnh nhân, tìm đúng lịch và mở Xem hồ sơ.
+4: Kiểm tra hồ sơ hiện tại được hiển thị đúng.
+5: Truy cập trực tiếp trang Khám bệnh bằng appointmentId của lịch đã hoàn thành.
+6: Kiểm tra hệ thống chặn tạo hồ sơ bệnh án mới.
+7: Mở lại hồ sơ và xác nhận dữ liệu cũ không thay đổi, lịch vẫn Đã hoàn thành.</t>
   </si>
   <si>
     <t>Bác sĩ xem được hồ sơ bệnh án hiện có. Khi truy cập trực tiếp trang Khám bệnh của lịch đã hoàn thành, hệ thống chặn truy cập và không hiển thị form tạo hồ sơ mới. Hồ sơ cũ không bị thay đổi và lịch vẫn ở trạng thái Đã hoàn thành.</t>
@@ -211,13 +208,12 @@
     <t>Bác sĩ xem lại đúng hồ sơ bệnh án của lịch đã hoàn thành.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch hẹn trạng thái Đã hoàn thành và đã có hồ sơ bệnh án.
-2: Đăng nhập bằng đúng tài khoản bác sĩ của lịch.
-3: Mở trang Lịch hẹn bệnh nhân.
-4: Tìm lịch TC-MEDICAL-005.
-5: Nhấn nút Xem hồ sơ.
-6: Kiểm tra thông tin bệnh nhân và bác sĩ.
-7: Kiểm tra chẩn đoán và hướng điều trị.</t>
+    <t>1: Chuẩn bị lịch Đã hoàn thành có hồ sơ và ghi nhận dữ liệu hồ sơ.
+2: Đăng nhập bằng bác sĩ phụ trách.
+3: Mở Lịch hẹn bệnh nhân và tìm đúng lịch.
+4: Nhấn Xem hồ sơ.
+5: Kiểm tra bệnh nhân, bác sĩ và appointmentId.
+6: Kiểm tra chẩn đoán và hướng điều trị khớp dữ liệu đã lưu.</t>
   </si>
   <si>
     <t>Hệ thống mở đúng hồ sơ bệnh án của lịch hẹn.
@@ -242,14 +238,14 @@
     <t>Bác sĩ cập nhật thành công hồ sơ bệnh án thuộc lịch của mình.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch hẹn Đã hoàn thành và đã có hồ sơ bệnh án.
-2: Đăng nhập bằng đúng tài khoản bác sĩ của lịch.
-3: Mở hồ sơ bệnh án của lịch TC-MEDICAL-006.
-4: Nhấn nút Cập nhật hồ sơ.
-5: Thay đổi chẩn đoán hoặc hướng điều trị.
-6: Nhấn nút Lưu cập nhật.
-7: Mở lại hồ sơ bệnh án.
-8: Kiểm tra nội dung và trạng thái lịch.</t>
+    <t>1: Chuẩn bị lịch Đã hoàn thành có hồ sơ và ghi nhận dữ liệu hồ sơ hiện tại.
+2: Đăng nhập bằng bác sĩ phụ trách và mở hồ sơ.
+3: Nhấn Cập nhật hồ sơ.
+4: Thay đổi chẩn đoán và hướng điều trị bằng dữ liệu mới.
+5: Nhấn Lưu cập nhật.
+6: Kiểm tra thông báo cập nhật thành công.
+7: Mở lại hồ sơ và kiểm tra nội dung mới.
+8: Kiểm tra hồ sơ vẫn thuộc cùng lịch, bệnh nhân, bác sĩ và lịch vẫn Đã hoàn thành.</t>
   </si>
   <si>
     <t>Hệ thống cập nhật hồ sơ bệnh án thành công.
@@ -271,16 +267,19 @@
     <t>Bác sĩ không được xem hồ sơ bệnh án không thuộc mình.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị hồ sơ bệnh án thuộc bác sĩ Ly Minh.
-2: Đăng nhập bằng tài khoản bác sĩ Tran Binh.
-3: Mở trang Lịch hẹn bệnh nhân.
-4: Kiểm tra lịch đó không xuất hiện trong danh sách.
-5: Nhập trực tiếp URL xem hồ sơ bệnh án.
-6: Kiểm tra nội dung trang được hiển thị.
-7: Kiểm tra dữ liệu hồ sơ có bị thay đổi hay không.</t>
+    <t>1: Chuẩn bị hồ sơ bệnh án thuộc Doctor A và ghi nhận appointmentId/medicalRecordId.
+2: Đăng nhập bằng Doctor B.
+3: Mở Lịch hẹn bệnh nhân.
+4: Kiểm tra lịch của Doctor A không xuất hiện trong danh sách Doctor B.
+5: Truy cập trực tiếp URL xem hồ sơ của Doctor A.
+6: Kiểm tra hệ thống chặn truy cập và không hiển thị dữ liệu hồ sơ.
+7: Đăng nhập lại Doctor A, mở hồ sơ và kiểm tra dữ liệu hồ sơ không thay đổi.</t>
   </si>
   <si>
-    <t>Hồ sơ không xuất hiện trong danh sách của bác sĩ Tran Binh. Khi truy cập trực tiếp URL, hệ thống chặn truy cập hoặc hiển thị thông báo không có quyền. Thông tin bệnh nhân và nội dung hồ sơ không được hiển thị. Dữ liệu hồ sơ không thay đổi.</t>
+    <t>Hồ sơ của Doctor A không xuất hiện trong danh sách của Doctor B.
+Khi Doctor B truy cập trực tiếp URL, hệ thống chặn truy cập hoặc hiển thị thông báo không có quyền.
+Thông tin bệnh nhân và nội dung hồ sơ không được hiển thị.
+Dữ liệu hồ sơ không thay đổi.</t>
   </si>
   <si>
     <t>TCMedical7</t>
@@ -298,21 +297,19 @@
     <t>Bác sĩ không được cập nhật hồ sơ bệnh án không thuộc mình.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị hồ sơ bệnh án của lịch TC-MEDICAL-008 thuộc bác sĩ Ly Minh.
-2: Đăng nhập bằng tài khoản bác sĩ Tran Binh.
-3: Nhập trực tiếp URL xem hồ sơ của lịch TC-MEDICAL-008.
-4: Kiểm tra thông tin bác sĩ phụ trách trên hồ sơ.
-5: Nhấn nút Cập nhật hồ sơ.
-6: Thay đổi chẩn đoán và hướng điều trị.
-7: Nhấn nút Lưu thay đổi.
-8: Kiểm tra thông báo và nội dung hồ sơ sau khi lưu.</t>
+    <t>1: Chuẩn bị hồ sơ bệnh án thuộc Doctor A và ghi nhận dữ liệu hiện tại.
+2: Đăng nhập bằng Doctor B.
+3: Truy cập trực tiếp URL hồ sơ của Doctor A.
+4: Kiểm tra hệ thống chặn truy cập; nếu trang hồ sơ được hiển thị thì Doctor B không có quyền cập nhật.
+5: Đăng xuất Doctor B và đăng nhập lại Doctor A.
+6: Mở lại hồ sơ bệnh án đã chuẩn bị.
+7: Kiểm tra chẩn đoán, hướng điều trị và bác sĩ phụ trách không thay đổi.</t>
   </si>
   <si>
-    <t>Hệ thống không cho phép bác sĩ Tran Binh cập nhật hồ sơ thuộc bác sĩ Ly Minh.
-Nút Cập nhật hồ sơ không được hiển thị hoặc thao tác cập nhật bị chặn.
-Hệ thống hiển thị thông báo không có quyền.
+    <t>Hệ thống không cho phép Doctor B cập nhật hồ sơ thuộc Doctor A.
+Doctor B bị chặn truy cập hoặc không có quyền sử dụng chức năng Cập nhật hồ sơ.
 Chẩn đoán và hướng điều trị cũ không bị thay đổi.
-Hồ sơ vẫn thuộc đúng bác sĩ Ly Minh.</t>
+Hồ sơ vẫn thuộc đúng Doctor A.</t>
   </si>
   <si>
     <t>TCMedical8_1, TCMedical8_2, TCMedical8_3</t>
@@ -330,14 +327,13 @@
     <t>Hủy cập nhật hồ sơ bệnh án không làm thay đổi dữ liệu đã lưu.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch TC-MEDICAL-009 ở trạng thái Đã hoàn thành và đã có hồ sơ bệnh án.
-2: Đăng nhập bằng đúng tài khoản bác sĩ Ly Minh.
-3: Mở trang Lịch hẹn bệnh nhân.
-4: Tìm lịch TC-MEDICAL-009 và nhấn nút Xem hồ sơ.
-5: Nhấn nút Cập nhật hồ sơ.
-6: Thay đổi chẩn đoán và hướng điều trị bằng nội dung mới.
-7: Nhấn nút Hủy.
-8: Kiểm tra nội dung hồ sơ bệnh án sau khi hủy.</t>
+    <t>1: Chuẩn bị hồ sơ bệnh án và ghi nhận chẩn đoán, hướng điều trị hiện tại.
+2: Đăng nhập bằng bác sĩ phụ trách và mở hồ sơ.
+3: Nhấn Cập nhật hồ sơ.
+4: Thay đổi chẩn đoán và hướng điều trị bằng dữ liệu mới.
+5: Nhấn Hủy.
+6: Kiểm tra form cập nhật được đóng và dữ liệu mới không được lưu.
+7: Kiểm tra hồ sơ vẫn giữ dữ liệu ban đầu và lịch vẫn Đã hoàn thành.</t>
   </si>
   <si>
     <t>Hệ thống hủy thao tác cập nhật và đóng form chỉnh sửa.
@@ -358,7 +354,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d\-m"/>
+    <numFmt numFmtId="165" formatCode="d\-m"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -373,10 +369,6 @@
       <name val="Tahoma"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="MS PGothic"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,6 +378,10 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="MS PGothic"/>
     </font>
     <font>
       <b/>
@@ -463,6 +459,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -487,9 +507,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -499,6 +517,26 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -538,109 +576,67 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -649,38 +645,38 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,7 +895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -922,9 +918,9 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -951,9 +947,9 @@
     </row>
     <row r="2" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -980,13 +976,13 @@
     </row>
     <row r="3" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
-      <c r="B3" s="43" t="s">
-        <v>15</v>
+      <c r="B3" s="33" t="s">
+        <v>2</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="38"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="35"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1013,13 +1009,13 @@
     </row>
     <row r="4" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="38"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="35"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1046,13 +1042,13 @@
     </row>
     <row r="5" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="38"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="35"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1079,13 +1075,13 @@
     </row>
     <row r="6" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" s="6">
         <v>7</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1116,13 +1112,13 @@
     </row>
     <row r="7" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6">
         <v>2</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" s="8">
         <v>9</v>
@@ -1181,39 +1177,39 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="32" t="s">
+      <c r="A9" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="41" t="s">
+      <c r="B9" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="C9" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="D9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="39" t="s">
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="39" t="s">
+      <c r="H9" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="L9" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="39" t="s">
+      <c r="M9" s="42" t="s">
         <v>19</v>
       </c>
       <c r="N9" s="3"/>
@@ -1232,19 +1228,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -1262,18 +1258,18 @@
     </row>
     <row r="11" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
@@ -1290,21 +1286,21 @@
       <c r="AA11" s="3"/>
     </row>
     <row r="12" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="38"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="35"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -1320,7 +1316,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="174" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>23</v>
       </c>
@@ -1330,11 +1326,11 @@
       <c r="C13" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="17" t="s">
         <v>27</v>
       </c>
@@ -1342,7 +1338,7 @@
         <v>46233</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>28</v>
@@ -1365,7 +1361,7 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="159" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>29</v>
       </c>
@@ -1375,11 +1371,11 @@
       <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
       <c r="G14" s="17" t="s">
         <v>33</v>
       </c>
@@ -1387,7 +1383,7 @@
         <v>46233</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>34</v>
@@ -1410,7 +1406,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>35</v>
       </c>
@@ -1420,11 +1416,11 @@
       <c r="C15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="17" t="s">
         <v>39</v>
       </c>
@@ -1432,7 +1428,7 @@
         <v>46233</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>40</v>
@@ -1465,11 +1461,11 @@
       <c r="C16" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="17" t="s">
         <v>45</v>
       </c>
@@ -1477,7 +1473,7 @@
         <v>46233</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>46</v>
@@ -1501,21 +1497,21 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="38"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="35"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -1541,11 +1537,11 @@
       <c r="C18" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="17" t="s">
         <v>52</v>
       </c>
@@ -1553,14 +1549,14 @@
         <v>46233</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>53</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="14"/>
-      <c r="M18" s="23"/>
+      <c r="M18" s="22"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -1577,21 +1573,21 @@
       <c r="AA18" s="3"/>
     </row>
     <row r="19" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="38"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="35"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -1607,7 +1603,7 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>55</v>
       </c>
@@ -1617,11 +1613,11 @@
       <c r="C20" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="25" t="s">
         <v>59</v>
       </c>
@@ -1629,7 +1625,7 @@
         <v>46233</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>60</v>
@@ -1652,7 +1648,7 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>61</v>
       </c>
@@ -1662,11 +1658,11 @@
       <c r="C21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="17" t="s">
         <v>65</v>
       </c>
@@ -1674,7 +1670,7 @@
         <v>46233</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>66</v>
@@ -1683,7 +1679,7 @@
         <v>46234</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M21" s="21" t="s">
         <v>67</v>
@@ -1703,7 +1699,7 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>68</v>
       </c>
@@ -1713,11 +1709,11 @@
       <c r="C22" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
       <c r="G22" s="17" t="s">
         <v>72</v>
       </c>
@@ -1725,7 +1721,7 @@
         <v>46233</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>73</v>
@@ -1734,7 +1730,7 @@
         <v>46234</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M22" s="21" t="s">
         <v>74</v>
@@ -1754,7 +1750,7 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="191.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>75</v>
       </c>
@@ -1764,11 +1760,11 @@
       <c r="C23" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
       <c r="G23" s="17" t="s">
         <v>79</v>
       </c>
@@ -1776,14 +1772,14 @@
         <v>46233</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J23" s="16" t="s">
         <v>80</v>
       </c>
       <c r="K23" s="18"/>
       <c r="L23" s="14"/>
-      <c r="M23" s="23"/>
+      <c r="M23" s="22"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1802,14 +1798,14 @@
     <row r="24" spans="1:27" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
       <c r="H24" s="28"/>
       <c r="I24" s="26"/>
-      <c r="J24" s="22"/>
+      <c r="J24" s="23"/>
       <c r="K24" s="28"/>
       <c r="L24" s="26"/>
       <c r="M24" s="29"/>
@@ -1917,7 +1913,7 @@
     </row>
     <row r="28" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
-      <c r="B28" s="22"/>
+      <c r="B28" s="23"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -2531,7 +2527,7 @@
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
-      <c r="G49" s="22"/>
+      <c r="G49" s="23"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
@@ -30163,18 +30159,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="D23:F23"/>
@@ -30191,19 +30175,31 @@
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
-    <hyperlink ref="G14" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
-    <hyperlink ref="G15" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
-    <hyperlink ref="G16" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
-    <hyperlink ref="G18" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
-    <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
-    <hyperlink ref="G21" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
-    <hyperlink ref="M21" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
-    <hyperlink ref="G22" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
-    <hyperlink ref="M22" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
-    <hyperlink ref="G23" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+    <hyperlink ref="G14" r:id="rId2" xr:uid="{00000000-0004-0000-0700-000001000000}"/>
+    <hyperlink ref="G15" r:id="rId3" xr:uid="{00000000-0004-0000-0700-000002000000}"/>
+    <hyperlink ref="G16" r:id="rId4" xr:uid="{00000000-0004-0000-0700-000003000000}"/>
+    <hyperlink ref="G18" r:id="rId5" xr:uid="{00000000-0004-0000-0700-000004000000}"/>
+    <hyperlink ref="G20" r:id="rId6" xr:uid="{00000000-0004-0000-0700-000005000000}"/>
+    <hyperlink ref="G21" r:id="rId7" xr:uid="{00000000-0004-0000-0700-000006000000}"/>
+    <hyperlink ref="M21" r:id="rId8" xr:uid="{00000000-0004-0000-0700-000007000000}"/>
+    <hyperlink ref="G22" r:id="rId9" xr:uid="{00000000-0004-0000-0700-000008000000}"/>
+    <hyperlink ref="M22" r:id="rId10" xr:uid="{00000000-0004-0000-0700-000009000000}"/>
+    <hyperlink ref="G23" r:id="rId11" xr:uid="{00000000-0004-0000-0700-00000A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestCases/Medical_TestCase.xlsx
+++ b/TestCases/Medical_TestCase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnNganh\SpringMediCareWeb-Selenium-Testing\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B562A163-4BA8-4962-9B81-22B7184455B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B79524-03D2-4B50-BB60-347EBA1ECE0D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12792" windowHeight="6960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MEDICAL" sheetId="8" r:id="rId1"/>
@@ -43,10 +43,10 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Pending</t>
+    <t>Fail</t>
   </si>
   <si>
-    <t>Fail</t>
+    <t>Pending</t>
   </si>
   <si>
     <t>Number of test cases:</t>
@@ -97,17 +97,18 @@
     <t>TC-MEDICAL-001</t>
   </si>
   <si>
-    <t>Bác sĩ tạo hồ sơ bệnh án thành công cho lịch hẹn đã được xác nhận.</t>
+    <t>Kiểm tra bác sĩ có thể tạo hồ sơ bệnh án thành công cho lịch hẹn đã được xác nhận.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị một lịch hẹn Đã xác nhận, chưa có hồ sơ bệnh án và ghi nhận thông tin lịch.
-2: Đăng nhập bằng bác sĩ phụ trách lịch hẹn.
-3: Mở trang Lịch hẹn bệnh nhân và tìm đúng lịch vừa chuẩn bị.
-4: Nhấn Khám bệnh.
-5: Kiểm tra trang Khám bệnh được mở đúng cho lịch hẹn.
-6: Nhập chẩn đoán và hướng điều trị hợp lệ.
-7: Nhấn Lưu hồ sơ bệnh án.
-8: Kiểm tra hồ sơ được tạo đúng và lịch chuyển sang Đã hoàn thành.</t>
+    <t>1: Chuẩn bị một lịch hẹn Đã xác nhận và chưa có hồ sơ bệnh án. 
+2: Đăng nhập bằng bác sĩ phụ trách lịch hẹn. 
+3: Mở trang Lịch hẹn bệnh nhân và tìm đúng lịch đã chuẩn bị. 
+4: Kiểm tra lịch ở trạng thái Đã xác nhận và có nút Khám bệnh. 
+5: Nhấn Khám bệnh. 
+6: Kiểm tra trang Khám bệnh được mở đúng cho lịch hẹn. 
+7: Nhập Chẩn đoán và Hướng điều trị hợp lệ. 
+8: Nhấn Lưu hồ sơ bệnh án. 
+9: Kiểm tra hồ sơ được tạo đúng và lịch chuyển sang Đã hoàn thành.</t>
   </si>
   <si>
     <t>Hệ thống tạo hồ sơ bệnh án thành công.
@@ -126,15 +127,16 @@
     <t>TC-MEDICAL-002</t>
   </si>
   <si>
-    <t>Không cho phép bác sĩ tạo hồ sơ bệnh án khi bỏ trống chẩn đoán.</t>
+    <t>Kiểm tra hệ thống không cho phép bác sĩ tạo hồ sơ bệnh án khi bỏ trống Chẩn đoán.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch Đã xác nhận, chưa có hồ sơ bệnh án.
-2: Đăng nhập bằng bác sĩ phụ trách và mở trang Khám bệnh của lịch.
-3: Để trống Chẩn đoán và nhập Hướng điều trị hợp lệ.
-4: Nhấn Lưu hồ sơ bệnh án.
-5: Kiểm tra thông báo validation của trường Chẩn đoán.
-6: Kiểm tra không tạo hồ sơ mới và lịch vẫn Đã xác nhận.</t>
+    <t>1: Chuẩn bị lịch hẹn Đã xác nhận và chưa có hồ sơ bệnh án. 
+2: Đăng nhập bằng bác sĩ phụ trách. 
+3: Mở trang Khám bệnh của lịch đã chuẩn bị. 
+4: Để trống Chẩn đoán và nhập Hướng điều trị hợp lệ. 
+5: Nhấn Lưu hồ sơ bệnh án. 
+6: Kiểm tra thông báo validation. 
+7: Kiểm tra hồ sơ không được tạo và lịch vẫn Đã xác nhận.</t>
   </si>
   <si>
     <t>Hệ thống hiển thị thông báo yêu cầu nhập đầy đủ chẩn đoán.
@@ -152,15 +154,16 @@
     <t>TC-MEDICAL-003</t>
   </si>
   <si>
-    <t>Không cho phép bác sĩ tạo hồ sơ bệnh án khi bỏ trống hướng điều trị.</t>
+    <t>Kiểm tra hệ thống không cho phép bác sĩ tạo hồ sơ bệnh án khi bỏ trống Hướng điều trị.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch Đã xác nhận, chưa có hồ sơ bệnh án.
-2: Đăng nhập bằng bác sĩ phụ trách và mở trang Khám bệnh của lịch.
-3: Nhập Chẩn đoán hợp lệ và để trống Hướng điều trị.
-4: Nhấn Lưu hồ sơ bệnh án.
-5: Kiểm tra thông báo validation của trường Hướng điều trị.
-6: Kiểm tra không tạo hồ sơ mới và lịch vẫn Đã xác nhận.</t>
+    <t>1: Chuẩn bị lịch hẹn Đã xác nhận và chưa có hồ sơ bệnh án. 
+2: Đăng nhập bằng bác sĩ phụ trách. 
+3: Mở trang Khám bệnh của lịch đã chuẩn bị. 
+4: Nhập Chẩn đoán hợp lệ và để trống Hướng điều trị. 
+5: Nhấn Lưu hồ sơ bệnh án. 
+6: Kiểm tra thông báo validation. 
+7: Kiểm tra hồ sơ không được tạo và lịch vẫn Đã xác nhận.</t>
   </si>
   <si>
     <t>Hệ thống hiển thị thông báo yêu cầu nhập đầy đủ hướng điều trị.
@@ -178,16 +181,17 @@
     <t>TC-MEDICAL-004</t>
   </si>
   <si>
-    <t>Không cho phép tạo thêm hồ sơ bệnh án cho lịch đã hoàn thành và đã có hồ sơ.</t>
+    <t>Kiểm tra hệ thống không cho phép bác sĩ tạo thêm hồ sơ bệnh án cho lịch hẹn đã hoàn thành và đã có hồ sơ bệnh án.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch Đã hoàn thành và đã có hồ sơ bệnh án; ghi nhận appointmentId và nội dung hồ sơ hiện tại.
-2: Đăng nhập bằng bác sĩ phụ trách.
-3: Mở Lịch hẹn bệnh nhân, tìm đúng lịch và mở Xem hồ sơ.
-4: Kiểm tra hồ sơ hiện tại được hiển thị đúng.
-5: Truy cập trực tiếp trang Khám bệnh bằng appointmentId của lịch đã hoàn thành.
-6: Kiểm tra hệ thống chặn tạo hồ sơ bệnh án mới.
-7: Mở lại hồ sơ và xác nhận dữ liệu cũ không thay đổi, lịch vẫn Đã hoàn thành.</t>
+    <t>1: Chuẩn bị lịch hẹn Đã hoàn thành và đã có hồ sơ bệnh án. 
+2: Đăng nhập bằng bác sĩ phụ trách. 
+3: Mở trang Lịch hẹn bệnh nhân và tìm đúng lịch đã chuẩn bị. 
+4: Kiểm tra lịch ở trạng thái Đã hoàn thành, có nút Xem hồ sơ và không còn nút Khám bệnh. 
+5: Nhấn Xem hồ sơ và kiểm tra hồ sơ hiện có được hiển thị đúng. 
+6: Truy cập trực tiếp trang Khám bệnh bằng appointmentId của lịch đã hoàn thành. 
+7: Kiểm tra hệ thống chặn thao tác khám bệnh và không hiển thị form tạo hồ sơ mới. 
+8: Mở lại hồ sơ và kiểm tra dữ liệu cũ không thay đổi.</t>
   </si>
   <si>
     <t>Bác sĩ xem được hồ sơ bệnh án hiện có. Khi truy cập trực tiếp trang Khám bệnh của lịch đã hoàn thành, hệ thống chặn truy cập và không hiển thị form tạo hồ sơ mới. Hồ sơ cũ không bị thay đổi và lịch vẫn ở trạng thái Đã hoàn thành.</t>
@@ -205,15 +209,17 @@
     <t>TC-MEDICAL-005</t>
   </si>
   <si>
-    <t>Bác sĩ xem lại đúng hồ sơ bệnh án của lịch đã hoàn thành.</t>
+    <t>Kiểm tra bác sĩ có thể xem đúng hồ sơ bệnh án của lịch hẹn đã hoàn thành.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch Đã hoàn thành có hồ sơ và ghi nhận dữ liệu hồ sơ.
-2: Đăng nhập bằng bác sĩ phụ trách.
-3: Mở Lịch hẹn bệnh nhân và tìm đúng lịch.
-4: Nhấn Xem hồ sơ.
-5: Kiểm tra bệnh nhân, bác sĩ và appointmentId.
-6: Kiểm tra chẩn đoán và hướng điều trị khớp dữ liệu đã lưu.</t>
+    <t>1: Chuẩn bị lịch Đã hoàn thành và đã có hồ sơ bệnh án. 
+2: Đăng nhập bằng bác sĩ phụ trách. 
+3: Mở trang Lịch hẹn bệnh nhân và tìm đúng lịch. 
+4: Kiểm tra lịch có nút Xem hồ sơ. 
+5: Nhấn Xem hồ sơ. 
+6: Kiểm tra appointmentId, bệnh nhân và bác sĩ phụ trách. 
+7: Kiểm tra Chẩn đoán và Hướng điều trị khớp dữ liệu đã lưu. 
+8: Kiểm tra thao tác xem hồ sơ không làm thay đổi dữ liệu hoặc trạng thái lịch.</t>
   </si>
   <si>
     <t>Hệ thống mở đúng hồ sơ bệnh án của lịch hẹn.
@@ -235,17 +241,19 @@
     <t>TC-MEDICAL-006</t>
   </si>
   <si>
-    <t>Bác sĩ cập nhật thành công hồ sơ bệnh án thuộc lịch của mình.</t>
+    <t>Kiểm tra bác sĩ có thể cập nhật thành công hồ sơ bệnh án thuộc lịch hẹn của mình.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị lịch Đã hoàn thành có hồ sơ và ghi nhận dữ liệu hồ sơ hiện tại.
-2: Đăng nhập bằng bác sĩ phụ trách và mở hồ sơ.
-3: Nhấn Cập nhật hồ sơ.
-4: Thay đổi chẩn đoán và hướng điều trị bằng dữ liệu mới.
-5: Nhấn Lưu cập nhật.
-6: Kiểm tra thông báo cập nhật thành công.
-7: Mở lại hồ sơ và kiểm tra nội dung mới.
-8: Kiểm tra hồ sơ vẫn thuộc cùng lịch, bệnh nhân, bác sĩ và lịch vẫn Đã hoàn thành.</t>
+    <t>1: Chuẩn bị lịch Đã hoàn thành, đã có hồ sơ và ghi nhận dữ liệu hiện tại. 
+2: Đăng nhập bằng bác sĩ phụ trách và mở hồ sơ. 
+3: Nhấn Cập nhật hồ sơ. 
+4: Kiểm tra form cập nhật hiển thị đúng dữ liệu hiện tại. 
+5: Thay đổi Chẩn đoán và Hướng điều trị. 
+6: Nhấn Lưu cập nhật. 
+7: Kiểm tra thông báo cập nhật thành công. 
+8: Mở lại hồ sơ và kiểm tra dữ liệu mới. 
+9: Kiểm tra hồ sơ vẫn thuộc cùng lịch hẹn, bệnh nhân và bác sĩ. 
+10: Kiểm tra hệ thống cập nhật hồ sơ hiện tại, không tạo thêm hồ sơ mới và lịch vẫn Đã hoàn thành.</t>
   </si>
   <si>
     <t>Hệ thống cập nhật hồ sơ bệnh án thành công.
@@ -264,16 +272,17 @@
     <t>TC-MEDICAL-007</t>
   </si>
   <si>
-    <t>Bác sĩ không được xem hồ sơ bệnh án không thuộc mình.</t>
+    <t>Kiểm tra bác sĩ khác không thể xem hồ sơ bệnh án không thuộc lịch hẹn của mình.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị hồ sơ bệnh án thuộc Doctor A và ghi nhận appointmentId/medicalRecordId.
-2: Đăng nhập bằng Doctor B.
-3: Mở Lịch hẹn bệnh nhân.
-4: Kiểm tra lịch của Doctor A không xuất hiện trong danh sách Doctor B.
-5: Truy cập trực tiếp URL xem hồ sơ của Doctor A.
-6: Kiểm tra hệ thống chặn truy cập và không hiển thị dữ liệu hồ sơ.
-7: Đăng nhập lại Doctor A, mở hồ sơ và kiểm tra dữ liệu hồ sơ không thay đổi.</t>
+    <t>1: Chuẩn bị hồ sơ bệnh án thuộc Doctor A và ghi nhận dữ liệu hiện tại. 
+2: Đăng nhập bằng Doctor B. 
+3: Mở trang Lịch hẹn bệnh nhân. 
+4: Kiểm tra lịch của Doctor A không xuất hiện trong danh sách của Doctor B. 
+5: Truy cập trực tiếp URL xem hồ sơ của Doctor A. 
+6: Kiểm tra hệ thống chặn truy cập và không hiển thị dữ liệu hồ sơ. 
+7: Đăng xuất Doctor B và đăng nhập lại Doctor A. 
+8: Mở lại hồ sơ và kiểm tra dữ liệu không thay đổi.</t>
   </si>
   <si>
     <t>Hồ sơ của Doctor A không xuất hiện trong danh sách của Doctor B.
@@ -294,16 +303,17 @@
     <t>TC-MEDICAL-008</t>
   </si>
   <si>
-    <t>Bác sĩ không được cập nhật hồ sơ bệnh án không thuộc mình.</t>
+    <t>Kiểm tra bác sĩ khác không thể cập nhật hồ sơ bệnh án không thuộc lịch hẹn của mình.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị hồ sơ bệnh án thuộc Doctor A và ghi nhận dữ liệu hiện tại.
-2: Đăng nhập bằng Doctor B.
-3: Truy cập trực tiếp URL hồ sơ của Doctor A.
-4: Kiểm tra hệ thống chặn truy cập; nếu trang hồ sơ được hiển thị thì Doctor B không có quyền cập nhật.
-5: Đăng xuất Doctor B và đăng nhập lại Doctor A.
-6: Mở lại hồ sơ bệnh án đã chuẩn bị.
-7: Kiểm tra chẩn đoán, hướng điều trị và bác sĩ phụ trách không thay đổi.</t>
+    <t>1: Chuẩn bị hồ sơ bệnh án thuộc Doctor A và ghi nhận dữ liệu hiện tại. 
+2: Đăng nhập bằng Doctor B. 
+3: Truy cập trực tiếp URL hồ sơ của Doctor A. 
+4: Kiểm tra hệ thống chặn truy cập và Doctor B không thể sử dụng chức năng Cập nhật hồ sơ. 
+5: Đăng xuất Doctor B và đăng nhập lại Doctor A. 
+6: Mở lại hồ sơ đã chuẩn bị. 
+7: Kiểm tra Chẩn đoán và Hướng điều trị không thay đổi. 
+8: Kiểm tra hồ sơ vẫn thuộc Doctor A và lịch vẫn Đã hoàn thành.</t>
   </si>
   <si>
     <t>Hệ thống không cho phép Doctor B cập nhật hồ sơ thuộc Doctor A.
@@ -324,16 +334,18 @@
     <t>TC-MEDICAL-009</t>
   </si>
   <si>
-    <t>Hủy cập nhật hồ sơ bệnh án không làm thay đổi dữ liệu đã lưu.</t>
+    <t>Kiểm tra thao tác Hủy cập nhật không làm thay đổi dữ liệu hồ sơ bệnh án đã lưu.</t>
   </si>
   <si>
-    <t>1: Chuẩn bị hồ sơ bệnh án và ghi nhận chẩn đoán, hướng điều trị hiện tại.
-2: Đăng nhập bằng bác sĩ phụ trách và mở hồ sơ.
-3: Nhấn Cập nhật hồ sơ.
-4: Thay đổi chẩn đoán và hướng điều trị bằng dữ liệu mới.
-5: Nhấn Hủy.
-6: Kiểm tra form cập nhật được đóng và dữ liệu mới không được lưu.
-7: Kiểm tra hồ sơ vẫn giữ dữ liệu ban đầu và lịch vẫn Đã hoàn thành.</t>
+    <t>1: Chuẩn bị hồ sơ bệnh án và ghi nhận dữ liệu hiện tại. 
+2: Đăng nhập bằng bác sĩ phụ trách và mở hồ sơ. 
+3: Nhấn Cập nhật hồ sơ. 
+4: Kiểm tra form cập nhật hiển thị đúng dữ liệu hiện tại. 
+5: Thay đổi Chẩn đoán và Hướng điều trị bằng dữ liệu mới. 
+6: Nhấn Hủy. 
+7: Kiểm tra form cập nhật được đóng và dữ liệu mới không được lưu. 
+8: Mở lại hồ sơ và kiểm tra dữ liệu ban đầu vẫn được giữ nguyên. 
+9: Kiểm tra hồ sơ vẫn thuộc đúng lịch hẹn, bệnh nhân, bác sĩ và lịch vẫn Đã hoàn thành.</t>
   </si>
   <si>
     <t>Hệ thống hủy thao tác cập nhật và đóng form chỉnh sửa.
@@ -904,7 +916,7 @@
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.109375" customWidth="1"/>
-    <col min="3" max="3" width="43.44140625" customWidth="1"/>
+    <col min="3" max="3" width="50.88671875" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="22.6640625" customWidth="1"/>
     <col min="8" max="8" width="20.109375" customWidth="1"/>
@@ -1081,7 +1093,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1112,7 +1124,7 @@
     </row>
     <row r="7" spans="1:27" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="6">
         <v>2</v>
@@ -1316,7 +1328,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="174" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="196.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>23</v>
       </c>
@@ -1451,7 +1463,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="183.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="210.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>41</v>
       </c>
@@ -1527,7 +1539,7 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="157.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>48</v>
       </c>
@@ -1603,7 +1615,7 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="186.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>55</v>
       </c>
@@ -1648,7 +1660,7 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="156" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>61</v>
       </c>
@@ -1670,7 +1682,7 @@
         <v>46233</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>66</v>
@@ -1699,7 +1711,7 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="165.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>68</v>
       </c>
@@ -1721,7 +1733,7 @@
         <v>46233</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>73</v>
@@ -1750,7 +1762,7 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="168.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>75</v>
       </c>
